--- a/results/gmac_snr3dB/gmac_snr3dB_classB_Ru28_Rv28_SCL32/classB_Ru28_Rv28_snr3dB_SCL_L32.xlsx
+++ b/results/gmac_snr3dB/gmac_snr3dB_classB_Ru28_Rv28_SCL32/classB_Ru28_Rv28_snr3dB_SCL_L32.xlsx
@@ -473,7 +473,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gaussian MAC — Class B, (Ru=0.28, Rv=0.28), SNR=3dB, SCL (L=32), pure_MC design</t>
+          <t>Gaussian MAC — Class B, (Ru=0.28, Rv=0.28), SNR=3dB, SCL (L=32)</t>
         </is>
       </c>
     </row>
